--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -276,7 +276,7 @@
 【JP Core仕様】画像結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -1123,10 +1123,10 @@
 </t>
   </si>
   <si>
-    <t>診断レポートが関係するヘルスケアイベントに関する情報</t>
-  </si>
-  <si>
-    <t>この診断レポートが関するヘルスケアイベント。</t>
+    <t>診断レポートが関係する診療イベントに関する情報</t>
+  </si>
+  <si>
+    <t>この診断レポートが関する診療イベント。</t>
   </si>
   <si>
     <t>これは通常、レポートの作成が発生するEncounterだが、一部のイベントはEncounterの正式な完了の前または後に開始される場合がある（例えば入院前の検査）。その場合でも（入院に関連して検査が行われる場合など）、Encounterのコンテキストに関連付けられる。  
